--- a/config/excel/quest.xlsx
+++ b/config/excel/quest.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\go\gforgame\config\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="quest" sheetId="1" r:id="rId1"/>
@@ -104,7 +109,7 @@
     <t>通过1关敌人。</t>
   </si>
   <si>
-    <t>money_500</t>
+    <t>item_1001_1</t>
   </si>
   <si>
     <t>英雄升级1次。</t>
@@ -204,7 +209,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,13 +220,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -724,133 +722,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -876,10 +874,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
